--- a/research/traditional_assets/database/data/canada/canada_office_equipment_services.xlsx
+++ b/research/traditional_assets/database/data/canada/canada_office_equipment_services.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.17</v>
+        <v>-0.158</v>
       </c>
       <c r="G2">
-        <v>-0.324</v>
+        <v>-0.3843416370106761</v>
       </c>
       <c r="H2">
-        <v>-0.324</v>
+        <v>-0.3843416370106761</v>
       </c>
       <c r="I2">
-        <v>-0.39</v>
+        <v>-0.5231316725978647</v>
       </c>
       <c r="J2">
-        <v>-0.39</v>
+        <v>-0.5231316725978647</v>
       </c>
       <c r="K2">
-        <v>-5.28</v>
+        <v>-6.52</v>
       </c>
       <c r="L2">
-        <v>-0.176</v>
+        <v>-0.2320284697508896</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.765</v>
+        <v>1.49</v>
       </c>
       <c r="V2">
-        <v>0.06652173913043478</v>
+        <v>4.005376344086022</v>
       </c>
       <c r="W2">
-        <v>-0.8585365853658536</v>
+        <v>-1.033280507131537</v>
       </c>
       <c r="X2">
-        <v>0.1031783845158074</v>
+        <v>2.115748051698541</v>
       </c>
       <c r="Y2">
-        <v>-0.9617149698816611</v>
+        <v>-3.149028558830078</v>
       </c>
       <c r="Z2">
-        <v>4.6875</v>
+        <v>1.240892029145507</v>
       </c>
       <c r="AA2">
-        <v>-1.828125</v>
+        <v>-0.6491499227202473</v>
       </c>
       <c r="AB2">
-        <v>0.05377678843022155</v>
+        <v>0.1518634275944204</v>
       </c>
       <c r="AC2">
-        <v>-1.881901788430221</v>
+        <v>-0.8010133503146677</v>
       </c>
       <c r="AD2">
-        <v>17.1</v>
+        <v>20.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>17.1</v>
+        <v>20.3</v>
       </c>
       <c r="AG2">
-        <v>16.335</v>
+        <v>18.81</v>
       </c>
       <c r="AH2">
-        <v>0.5979020979020979</v>
+        <v>0.9820046439628483</v>
       </c>
       <c r="AI2">
-        <v>0.730457069628364</v>
+        <v>0.9896163408570174</v>
       </c>
       <c r="AJ2">
-        <v>0.5868510867612718</v>
+        <v>0.980606818892712</v>
       </c>
       <c r="AK2">
-        <v>0.7213512916758666</v>
+        <v>0.9888030279135782</v>
       </c>
       <c r="AL2">
-        <v>0.658</v>
+        <v>1.33</v>
       </c>
       <c r="AM2">
-        <v>0.658</v>
+        <v>1.33</v>
       </c>
       <c r="AN2">
-        <v>-1.628571428571429</v>
+        <v>-1.492647058823529</v>
       </c>
       <c r="AO2">
-        <v>-17.78115501519757</v>
+        <v>-11.05263157894737</v>
       </c>
       <c r="AP2">
-        <v>-1.555714285714286</v>
+        <v>-1.383088235294118</v>
       </c>
       <c r="AQ2">
-        <v>-17.78115501519757</v>
+        <v>-11.05263157894737</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.17</v>
+        <v>-0.158</v>
       </c>
       <c r="G3">
-        <v>-0.324</v>
+        <v>-0.3843416370106761</v>
       </c>
       <c r="H3">
-        <v>-0.324</v>
+        <v>-0.3843416370106761</v>
       </c>
       <c r="I3">
-        <v>-0.39</v>
+        <v>-0.5231316725978647</v>
       </c>
       <c r="J3">
-        <v>-0.39</v>
+        <v>-0.5231316725978647</v>
       </c>
       <c r="K3">
-        <v>-5.28</v>
+        <v>-6.52</v>
       </c>
       <c r="L3">
-        <v>-0.176</v>
+        <v>-0.2320284697508896</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.765</v>
+        <v>1.49</v>
       </c>
       <c r="V3">
-        <v>0.06652173913043478</v>
+        <v>4.005376344086022</v>
       </c>
       <c r="W3">
-        <v>-0.8585365853658536</v>
+        <v>-1.033280507131537</v>
       </c>
       <c r="X3">
-        <v>0.1031783845158074</v>
+        <v>2.115748051698541</v>
       </c>
       <c r="Y3">
-        <v>-0.9617149698816611</v>
+        <v>-3.149028558830078</v>
       </c>
       <c r="Z3">
-        <v>4.6875</v>
+        <v>1.240892029145507</v>
       </c>
       <c r="AA3">
-        <v>-1.828125</v>
+        <v>-0.6491499227202473</v>
       </c>
       <c r="AB3">
-        <v>0.05377678843022155</v>
+        <v>0.1518634275944204</v>
       </c>
       <c r="AC3">
-        <v>-1.881901788430221</v>
+        <v>-0.8010133503146677</v>
       </c>
       <c r="AD3">
-        <v>17.1</v>
+        <v>20.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>17.1</v>
+        <v>20.3</v>
       </c>
       <c r="AG3">
-        <v>16.335</v>
+        <v>18.81</v>
       </c>
       <c r="AH3">
-        <v>0.5979020979020979</v>
+        <v>0.9820046439628483</v>
       </c>
       <c r="AI3">
-        <v>0.730457069628364</v>
+        <v>0.9896163408570174</v>
       </c>
       <c r="AJ3">
-        <v>0.5868510867612718</v>
+        <v>0.980606818892712</v>
       </c>
       <c r="AK3">
-        <v>0.7213512916758666</v>
+        <v>0.9888030279135782</v>
       </c>
       <c r="AL3">
-        <v>0.658</v>
+        <v>1.33</v>
       </c>
       <c r="AM3">
-        <v>0.658</v>
+        <v>1.33</v>
       </c>
       <c r="AN3">
-        <v>-1.628571428571429</v>
+        <v>-1.492647058823529</v>
       </c>
       <c r="AO3">
-        <v>-17.78115501519757</v>
+        <v>-11.05263157894737</v>
       </c>
       <c r="AP3">
-        <v>-1.555714285714286</v>
+        <v>-1.383088235294118</v>
       </c>
       <c r="AQ3">
-        <v>-17.78115501519757</v>
+        <v>-11.05263157894737</v>
       </c>
     </row>
   </sheetData>
